--- a/OUTPUT/direct_P0ACJ8_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/OUTPUT/direct_P0ACJ8_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.2862</v>
+        <v>0.2862854858056778</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.165</v>
+        <v>0.1651339464214314</v>
       </c>
     </row>
   </sheetData>
